--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.9870171390857</v>
+        <v>4.710390285101427</v>
       </c>
       <c r="D2" t="n">
-        <v>28.78959171361533</v>
+        <v>4.678308653462491</v>
       </c>
       <c r="E2" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F2" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.2433733055492</v>
+        <v>11.90204816215175</v>
       </c>
       <c r="D3" t="n">
-        <v>73.46148721370191</v>
+        <v>11.93749167222656</v>
       </c>
       <c r="E3" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F3" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.37774033043549</v>
+        <v>6.236382803695767</v>
       </c>
       <c r="D4" t="n">
-        <v>38.6579112312391</v>
+        <v>6.281910575076354</v>
       </c>
       <c r="E4" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F4" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.53745130363372</v>
+        <v>9.34983583684048</v>
       </c>
       <c r="D5" t="n">
-        <v>57.40733861053798</v>
+        <v>9.328692524212423</v>
       </c>
       <c r="E5" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F5" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.10910085720425</v>
+        <v>7.655228889295691</v>
       </c>
       <c r="D6" t="n">
-        <v>47.02251444054334</v>
+        <v>7.641158596588293</v>
       </c>
       <c r="E6" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F6" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.68142478428576</v>
+        <v>6.448231527446437</v>
       </c>
       <c r="D7" t="n">
-        <v>45.44928403981648</v>
+        <v>7.385508656470178</v>
       </c>
       <c r="E7" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F7" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.13245599393639</v>
+        <v>4.084024099014663</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86175589319629</v>
+        <v>4.040035332644398</v>
       </c>
       <c r="E8" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>2.304873664194443</v>
+        <v>0.374541970431597</v>
       </c>
       <c r="D9" t="n">
-        <v>14.6347175258595</v>
+        <v>2.378141597952169</v>
       </c>
       <c r="E9" t="n">
-        <v>20.06843992168571</v>
+        <v>3.261121487273928</v>
       </c>
       <c r="F9" t="n">
-        <v>17.6370128889002</v>
+        <v>2.866014594446283</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
